--- a/Preliminary Data/two forces (SVD optimized)/working beam don't delete.xlsx
+++ b/Preliminary Data/two forces (SVD optimized)/working beam don't delete.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahj\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Preliminary Data/two forces (SVD optimized)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D33812-2DE6-43A2-8F31-0CF157942B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{B0D33812-2DE6-43A2-8F31-0CF157942B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC9BA393-A61F-458F-8107-CEFE357CA8B9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D5B36658-BC8B-4D47-B630-E06D74D74F70}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D5B36658-BC8B-4D47-B630-E06D74D74F70}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -416,10 +416,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE21358-104C-4D35-9A74-24743A0F8E34}">
-  <dimension ref="A3:V6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:AO9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -487,7 +487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2.0999999999999999E-3</v>
       </c>
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -617,7 +617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>2.0999999999999999E-3</v>
       </c>
@@ -680,6 +680,128 @@
       </c>
       <c r="V6" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="C9">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="D9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E9">
+        <v>2E-3</v>
+      </c>
+      <c r="F9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G9">
+        <v>1.9E-3</v>
+      </c>
+      <c r="H9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="I9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="K9">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="L9">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="M9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="N9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="O9">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="P9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="R9">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="S9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="T9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="U9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="V9">
+        <v>1.5E-3</v>
+      </c>
+      <c r="W9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="X9">
+        <v>1.9E-3</v>
+      </c>
+      <c r="Y9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Z9">
+        <v>2E-3</v>
+      </c>
+      <c r="AA9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AB9">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="AC9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AD9">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="AE9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AF9">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="AG9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AH9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AI9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AJ9">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="AK9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AL9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AM9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AN9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AO9">
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>

--- a/Preliminary Data/two forces (SVD optimized)/working beam don't delete.xlsx
+++ b/Preliminary Data/two forces (SVD optimized)/working beam don't delete.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Preliminary Data/two forces (SVD optimized)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{B0D33812-2DE6-43A2-8F31-0CF157942B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC9BA393-A61F-458F-8107-CEFE357CA8B9}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{B0D33812-2DE6-43A2-8F31-0CF157942B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9432BAEA-7F05-4885-9A1C-239ABE380D3F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D5B36658-BC8B-4D47-B630-E06D74D74F70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D5B36658-BC8B-4D47-B630-E06D74D74F70}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
   <si>
     <t>[</t>
   </si>
@@ -45,6 +45,24 @@
   </si>
   <si>
     <t>]</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>F_value</t>
+  </si>
+  <si>
+    <t>x_value</t>
+  </si>
+  <si>
+    <t>0.1 separation PLA</t>
+  </si>
+  <si>
+    <t>0.1 separation PLA constraint not enforced</t>
+  </si>
+  <si>
+    <t>0.02 separation PLA</t>
   </si>
 </sst>
 </file>
@@ -80,8 +98,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -97,6 +116,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,63 +439,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE21358-104C-4D35-9A74-24743A0F8E34}">
-  <dimension ref="A3:AO9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:BN19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C3">
-        <v>4.0000000000000001E-3</v>
+    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>0</v>
       </c>
       <c r="D3">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="E3">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="F3">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="G3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="H3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="I3">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="H3">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="I3">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="J3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="L3">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="K3">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="L3">
+      <c r="M3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="N3">
         <v>1.5E-3</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>1.9E-3</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>2E-3</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="Q3">
-        <v>3.5999999999999999E-3</v>
-      </c>
-      <c r="R3">
-        <v>4.0000000000000001E-3</v>
       </c>
       <c r="S3">
         <v>3.5999999999999999E-3</v>
@@ -481,42 +513,42 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="U3">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="V3" t="s">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="V3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="W3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="X3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="B4">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="D4">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>2E-3</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>1.9E-3</v>
       </c>
-      <c r="E4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="F4">
+      <c r="G4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="H4">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="G4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J4">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="I4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="J4">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="K4">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="L4">
         <v>1.2999999999999999E-3</v>
@@ -537,7 +569,7 @@
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="R4">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="S4">
         <v>1.2999999999999999E-3</v>
@@ -546,63 +578,63 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="U4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="V4" t="s">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="V4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="W4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="X4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="B5">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C5">
-        <v>4.0000000000000001E-3</v>
-      </c>
+    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
       <c r="D5">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="E5">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="F5">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="G5">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="H5">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="I5">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="H5">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="I5">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="J5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K5">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="L5">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="K5">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="L5">
+      <c r="M5">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="N5">
         <v>1.5E-3</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>1.9E-3</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>2E-3</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="P5">
+      <c r="R5">
         <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="Q5">
-        <v>3.5999999999999999E-3</v>
-      </c>
-      <c r="R5">
-        <v>4.0000000000000001E-3</v>
       </c>
       <c r="S5">
         <v>3.5999999999999999E-3</v>
@@ -611,42 +643,42 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="U5">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="V5" t="s">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="V5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="W5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="X5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="B6">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="D6">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>2E-3</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>1.9E-3</v>
       </c>
-      <c r="E6">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="F6">
+      <c r="G6">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="H6">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="G6">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="I6">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="J6">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="K6">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="L6">
         <v>1.2999999999999999E-3</v>
@@ -667,7 +699,7 @@
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="R6">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="S6">
         <v>1.2999999999999999E-3</v>
@@ -676,132 +708,1101 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="U6">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="V6" t="s">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="V6">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="W6">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="X6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
-      <c r="B9">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C9">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E9">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="D9">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="E9">
+      <c r="F9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G9">
         <v>2E-3</v>
       </c>
-      <c r="F9">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="G9">
+      <c r="H9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I9">
         <v>1.9E-3</v>
       </c>
-      <c r="H9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="I9">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="J9">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="K9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="M9">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="M9">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="N9">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="O9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="P9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Q9">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="P9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q9">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="R9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="S9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="T9">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="S9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="T9">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="U9">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="V9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="W9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="X9">
         <v>1.5E-3</v>
       </c>
-      <c r="W9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="X9">
+      <c r="Y9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Z9">
         <v>1.9E-3</v>
       </c>
-      <c r="Y9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Z9">
+      <c r="AA9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AB9">
         <v>2E-3</v>
       </c>
-      <c r="AA9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AB9">
+      <c r="AC9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AD9">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="AC9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AD9">
+      <c r="AE9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AF9">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="AE9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AF9">
+      <c r="AG9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AH9">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="AG9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AH9">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="AI9">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="AJ9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AK9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AL9">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="AK9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AL9">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="AM9">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="AN9">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="AO9">
         <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AP9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AQ9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E11">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="H11">
+        <v>2E-3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K11">
+        <v>1.9E-3</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="N11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q11">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="T11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="W11">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Z11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="AC11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AF11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>1.5E-3</v>
+      </c>
+      <c r="AI11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>1.9E-3</v>
+      </c>
+      <c r="AL11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>2E-3</v>
+      </c>
+      <c r="AO11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="AR11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="AU11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="AX11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BA11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="BD11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BG11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BJ11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E13">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="F13">
+        <v>0.2</v>
+      </c>
+      <c r="G13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="H13">
+        <v>2E-3</v>
+      </c>
+      <c r="I13">
+        <v>0.4</v>
+      </c>
+      <c r="J13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K13">
+        <v>1.9E-3</v>
+      </c>
+      <c r="L13">
+        <v>0.6</v>
+      </c>
+      <c r="M13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="N13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="O13">
+        <v>0.7</v>
+      </c>
+      <c r="P13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q13">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="R13">
+        <v>0.8</v>
+      </c>
+      <c r="S13">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="T13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="U13">
+        <v>0.9</v>
+      </c>
+      <c r="V13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="W13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Z13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AA13">
+        <v>1.2</v>
+      </c>
+      <c r="AB13">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="AC13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AD13">
+        <v>1.4</v>
+      </c>
+      <c r="AE13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AF13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>1.5E-3</v>
+      </c>
+      <c r="AI13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>1.9E-3</v>
+      </c>
+      <c r="AL13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>2E-3</v>
+      </c>
+      <c r="AO13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="AR13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="AU13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="AX13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BA13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="BD13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BG13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BJ13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <f>-1.8411</f>
+        <v>-1.8411</v>
+      </c>
+      <c r="C15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>4.9917579159516898E-3</v>
+      </c>
+      <c r="E15">
+        <v>1.69595975098749E-3</v>
+      </c>
+      <c r="F15">
+        <v>1.53974225422019</v>
+      </c>
+      <c r="G15">
+        <v>4.9938175453636902E-3</v>
+      </c>
+      <c r="H15">
+        <v>1.52734599893879E-3</v>
+      </c>
+      <c r="I15">
+        <v>2.6425776191910102</v>
+      </c>
+      <c r="J15">
+        <v>4.99927311046202E-3</v>
+      </c>
+      <c r="K15">
+        <v>4.98549363194975E-3</v>
+      </c>
+      <c r="L15">
+        <v>1.38776431390161</v>
+      </c>
+      <c r="M15">
+        <v>4.9464215982714596E-3</v>
+      </c>
+      <c r="N15">
+        <v>4.2953197422253703E-3</v>
+      </c>
+      <c r="O15">
+        <v>2.4093315068202998</v>
+      </c>
+      <c r="P15">
+        <v>1.8189321702073E-3</v>
+      </c>
+      <c r="Q15">
+        <v>1.0583880824811701E-3</v>
+      </c>
+      <c r="R15">
+        <v>2.8841487871146998</v>
+      </c>
+      <c r="S15">
+        <v>2.3829718197879201E-3</v>
+      </c>
+      <c r="T15">
+        <v>2.2888507753033001E-3</v>
+      </c>
+      <c r="U15">
+        <v>1.2064090503867599</v>
+      </c>
+      <c r="V15">
+        <v>2.18903065690902E-3</v>
+      </c>
+      <c r="W15">
+        <v>1.77999436998265E-3</v>
+      </c>
+      <c r="X15">
+        <v>2.7574092757572499</v>
+      </c>
+      <c r="Y15">
+        <v>1.00036787367038E-3</v>
+      </c>
+      <c r="Z15">
+        <v>1.2211658668088701E-3</v>
+      </c>
+      <c r="AA15">
+        <v>1.2277843263981199E-3</v>
+      </c>
+      <c r="AB15">
+        <v>1.0004226815027899E-3</v>
+      </c>
+      <c r="AC15">
+        <v>1.43424370261431E-3</v>
+      </c>
+      <c r="AD15">
+        <v>2.6156269221677699</v>
+      </c>
+      <c r="AE15">
+        <v>1.3631860047426799E-3</v>
+      </c>
+      <c r="AF15">
+        <v>1.01709818146589E-3</v>
+      </c>
+      <c r="AG15">
+        <v>1.17882694253418</v>
+      </c>
+      <c r="AH15">
+        <v>1.60603867362093E-3</v>
+      </c>
+      <c r="AI15">
+        <v>1.2035585878934401E-3</v>
+      </c>
+      <c r="AJ15">
+        <v>1.08236895450346</v>
+      </c>
+      <c r="AK15">
+        <v>4.99361164120598E-3</v>
+      </c>
+      <c r="AL15">
+        <v>1.7043963847344001E-3</v>
+      </c>
+      <c r="AM15">
+        <v>1.6324039952234299</v>
+      </c>
+      <c r="AN15">
+        <v>4.0604398977100503E-3</v>
+      </c>
+      <c r="AO15">
+        <v>1.0095972253412501E-3</v>
+      </c>
+      <c r="AP15">
+        <v>1.0896067672312</v>
+      </c>
+      <c r="AQ15">
+        <v>4.9928114567989899E-3</v>
+      </c>
+      <c r="AR15">
+        <v>4.87339902093101E-3</v>
+      </c>
+      <c r="AS15">
+        <v>0.927457951913082</v>
+      </c>
+      <c r="AT15">
+        <v>4.9907424522168198E-3</v>
+      </c>
+      <c r="AU15">
+        <v>4.9994982391283497E-3</v>
+      </c>
+      <c r="AV15">
+        <v>2.41775361095609</v>
+      </c>
+      <c r="AW15">
+        <v>4.9966924318709197E-3</v>
+      </c>
+      <c r="AX15">
+        <v>4.9981453308859001E-3</v>
+      </c>
+      <c r="AY15">
+        <v>1.49562976361246</v>
+      </c>
+      <c r="AZ15">
+        <v>4.7871529198324804E-3</v>
+      </c>
+      <c r="BA15">
+        <v>4.9957628048072199E-3</v>
+      </c>
+      <c r="BB15">
+        <v>2.7581032798254501</v>
+      </c>
+      <c r="BC15">
+        <v>4.9932653830236703E-3</v>
+      </c>
+      <c r="BD15">
+        <v>4.99747273573177E-3</v>
+      </c>
+      <c r="BE15">
+        <v>2.2622097362276201</v>
+      </c>
+      <c r="BF15">
+        <v>4.7896767299011904E-3</v>
+      </c>
+      <c r="BG15">
+        <v>4.0944478477437001E-3</v>
+      </c>
+      <c r="BH15">
+        <v>0.28910723808435501</v>
+      </c>
+      <c r="BI15">
+        <v>4.08738384131253E-3</v>
+      </c>
+      <c r="BJ15">
+        <v>4.9994042539320202E-3</v>
+      </c>
+      <c r="BK15">
+        <v>0.86791073471472502</v>
+      </c>
+      <c r="BL15" t="s">
+        <v>2</v>
+      </c>
+      <c r="BN15">
+        <f>-1.8411</f>
+        <v>-1.8411</v>
+      </c>
+    </row>
+    <row r="17" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-2.0819999999999999</v>
+      </c>
+      <c r="C17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2.2720000000000001E-3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1.125</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2.3340000000000001E-3</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4.5669999999999999E-3</v>
+      </c>
+      <c r="I17" s="1">
+        <v>3.7940000000000002E-2</v>
+      </c>
+      <c r="J17" s="1">
+        <v>3.4190000000000002E-3</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1.193E-3</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2.161</v>
+      </c>
+      <c r="M17" s="1">
+        <v>1.841E-3</v>
+      </c>
+      <c r="N17" s="1">
+        <v>4.5189999999999996E-3</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0.54369999999999996</v>
+      </c>
+      <c r="P17" s="1">
+        <v>4.6109999999999996E-3</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>3.885E-3</v>
+      </c>
+      <c r="R17" s="1">
+        <v>2.09</v>
+      </c>
+      <c r="S17" s="1">
+        <v>2.085E-3</v>
+      </c>
+      <c r="T17" s="1">
+        <v>1.5659999999999999E-3</v>
+      </c>
+      <c r="U17" s="1">
+        <v>0.59470000000000001</v>
+      </c>
+      <c r="V17" s="1">
+        <v>1.1900000000000001E-3</v>
+      </c>
+      <c r="W17" s="1">
+        <v>3.0969999999999999E-3</v>
+      </c>
+      <c r="X17" s="1">
+        <v>1.867</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>2.9320000000000001E-3</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>2.0539999999999998</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AC17" s="1">
+        <v>3.3449999999999999E-3</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>1.8759999999999999</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AF17" s="1">
+        <v>3.62E-3</v>
+      </c>
+      <c r="AG17" s="1">
+        <v>2.0510000000000002</v>
+      </c>
+      <c r="AH17" s="1">
+        <v>4.5050000000000003E-3</v>
+      </c>
+      <c r="AI17" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AJ17" s="1">
+        <v>2.5649999999999999</v>
+      </c>
+      <c r="AK17" s="1">
+        <v>4.8269999999999997E-3</v>
+      </c>
+      <c r="AL17" s="1">
+        <v>4.0629999999999998E-3</v>
+      </c>
+      <c r="AM17" s="1">
+        <v>1.7929999999999999</v>
+      </c>
+      <c r="AN17" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AO17" s="1">
+        <v>4.8560000000000001E-3</v>
+      </c>
+      <c r="AP17" s="1">
+        <v>3.0470000000000002</v>
+      </c>
+      <c r="AQ17" s="1">
+        <v>4.6629999999999996E-3</v>
+      </c>
+      <c r="AR17" s="1">
+        <v>2.8370000000000001E-3</v>
+      </c>
+      <c r="AS17" s="1">
+        <v>2.4049999999999998</v>
+      </c>
+      <c r="AT17" s="1">
+        <v>3.261E-3</v>
+      </c>
+      <c r="AU17" s="1">
+        <v>4.3699999999999998E-3</v>
+      </c>
+      <c r="AV17" s="1">
+        <v>1.845</v>
+      </c>
+      <c r="AW17" s="1">
+        <v>2.3240000000000001E-3</v>
+      </c>
+      <c r="AX17" s="1">
+        <v>2.9780000000000002E-3</v>
+      </c>
+      <c r="AY17" s="1">
+        <v>0.54490000000000005</v>
+      </c>
+      <c r="AZ17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BA17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BB17" s="1">
+        <v>0.24940000000000001</v>
+      </c>
+      <c r="BC17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BD17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BE17" s="1">
+        <v>2.8889999999999998</v>
+      </c>
+      <c r="BF17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BG17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BH17" s="1">
+        <v>0.27689999999999998</v>
+      </c>
+      <c r="BI17" s="1">
+        <v>1.1349999999999999E-3</v>
+      </c>
+      <c r="BJ17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BK17" s="1">
+        <v>1.474</v>
+      </c>
+      <c r="BL17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:64" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="1">
+        <v>-0.67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4.8609999999999999E-3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2.9729999999999999E-3</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2.4969999999999999</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2.7460000000000002E-3</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1.2769999999999999E-3</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0.26290000000000002</v>
+      </c>
+      <c r="J19" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K19" s="1">
+        <v>2.0669999999999998E-3</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2.8730000000000002</v>
+      </c>
+      <c r="M19" s="1">
+        <v>3.6280000000000001E-3</v>
+      </c>
+      <c r="N19" s="1">
+        <v>2.6900000000000001E-3</v>
+      </c>
+      <c r="O19" s="1">
+        <v>1.8069999999999999</v>
+      </c>
+      <c r="P19" s="1">
+        <v>3.5729999999999998E-3</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>3.5729999999999998E-3</v>
+      </c>
+      <c r="R19" s="1">
+        <v>1.4630000000000001</v>
+      </c>
+      <c r="S19" s="1">
+        <v>4.3200000000000001E-3</v>
+      </c>
+      <c r="T19" s="1">
+        <v>2.6900000000000001E-3</v>
+      </c>
+      <c r="U19" s="1">
+        <v>2.069</v>
+      </c>
+      <c r="V19" s="1">
+        <v>2.6900000000000001E-3</v>
+      </c>
+      <c r="W19" s="1">
+        <v>4.7169999999999998E-3</v>
+      </c>
+      <c r="X19" s="1">
+        <v>1.2849999999999999</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>2.4529999999999999E-3</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AA19" s="1">
+        <v>2.278</v>
+      </c>
+      <c r="AB19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AC19" s="1">
+        <v>3.176E-3</v>
+      </c>
+      <c r="AD19" s="1">
+        <v>0.39779999999999999</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>4.8609999999999999E-3</v>
+      </c>
+      <c r="AF19" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AG19" s="1">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="AH19" s="1">
+        <v>1.0250000000000001E-3</v>
+      </c>
+      <c r="AI19" s="1">
+        <v>3.3540000000000002E-3</v>
+      </c>
+      <c r="AJ19" s="1">
+        <v>3.0339999999999998</v>
+      </c>
+      <c r="AK19" s="1">
+        <v>4.8609999999999999E-3</v>
+      </c>
+      <c r="AL19" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AM19" s="1">
+        <v>2.9279999999999999</v>
+      </c>
+      <c r="AN19" s="1">
+        <v>4.8609999999999999E-3</v>
+      </c>
+      <c r="AO19" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AP19" s="1">
+        <v>0.63970000000000005</v>
+      </c>
+      <c r="AQ19" s="1">
+        <v>3.5729999999999998E-3</v>
+      </c>
+      <c r="AR19" s="1">
+        <v>3.5729999999999998E-3</v>
+      </c>
+      <c r="AS19" s="1">
+        <v>1.375</v>
+      </c>
+      <c r="AT19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AU19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AV19" s="1">
+        <v>1.9390000000000001</v>
+      </c>
+      <c r="AW19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AX19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AY19" s="1">
+        <v>1.208</v>
+      </c>
+      <c r="AZ19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BA19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BB19" s="1">
+        <v>0.75949999999999995</v>
+      </c>
+      <c r="BC19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BD19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BE19" s="1">
+        <v>2.8410000000000002</v>
+      </c>
+      <c r="BF19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BG19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BH19" s="1">
+        <v>2.5339999999999998</v>
+      </c>
+      <c r="BI19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BJ19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BK19" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Preliminary Data/two forces (SVD optimized)/working beam don't delete.xlsx
+++ b/Preliminary Data/two forces (SVD optimized)/working beam don't delete.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Preliminary Data/two forces (SVD optimized)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{B0D33812-2DE6-43A2-8F31-0CF157942B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9432BAEA-7F05-4885-9A1C-239ABE380D3F}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{B0D33812-2DE6-43A2-8F31-0CF157942B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1815389-A39C-468B-9A82-235CFA0B7407}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D5B36658-BC8B-4D47-B630-E06D74D74F70}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D5B36658-BC8B-4D47-B630-E06D74D74F70}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="11">
   <si>
     <t>[</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>]</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>F_value</t>
@@ -63,6 +60,15 @@
   </si>
   <si>
     <t>0.02 separation PLA</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>mean min singular values</t>
+  </si>
+  <si>
+    <t>Min s separation (cm)</t>
   </si>
 </sst>
 </file>
@@ -116,6 +122,1048 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Effect of Force Separation on Average SNR</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="254000" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="38100">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$17:$B$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$17:$C$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2.0819999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.67</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6969-4B79-9AFB-C03678D5220A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="163431551"/>
+        <c:axId val="163430111"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="163431551"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400"/>
+                  <a:t>Minimum</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" baseline="0"/>
+                  <a:t> Force Separation (cm)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1400"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="163430111"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="163430111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400"/>
+                  <a:t>Average</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" baseline="0"/>
+                  <a:t> SNR</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1400"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="163431551"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>923925</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95724BF0-7A7C-1BA7-FBF1-61616826F40F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -439,78 +1487,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE21358-104C-4D35-9A74-24743A0F8E34}">
-  <dimension ref="A1:BN19"/>
+  <dimension ref="A1:BP27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="E3">
-        <v>4.0000000000000001E-3</v>
+    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>0</v>
       </c>
       <c r="F3">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="G3">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="H3">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="I3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="J3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="K3">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="J3">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="K3">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="L3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="N3">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="M3">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="N3">
+      <c r="O3">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="P3">
         <v>1.5E-3</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>1.9E-3</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>2E-3</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="S3">
-        <v>3.5999999999999999E-3</v>
-      </c>
-      <c r="T3">
-        <v>4.0000000000000001E-3</v>
       </c>
       <c r="U3">
         <v>3.5999999999999999E-3</v>
@@ -519,42 +1569,42 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="W3">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="X3" t="s">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="X3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Y3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Z3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="D4">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="F4">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>2E-3</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>1.9E-3</v>
       </c>
-      <c r="G4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J4">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="I4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="J4">
+      <c r="K4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L4">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="K4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="L4">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="M4">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="N4">
         <v>1.2999999999999999E-3</v>
@@ -575,7 +1625,7 @@
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="T4">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="U4">
         <v>1.2999999999999999E-3</v>
@@ -584,63 +1634,63 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="W4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="X4" t="s">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="X4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Y4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Z4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="D5">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="E5">
-        <v>4.0000000000000001E-3</v>
-      </c>
+    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
       <c r="F5">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="G5">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="H5">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="I5">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="J5">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="K5">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="J5">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="K5">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="L5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M5">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="N5">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="M5">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="N5">
+      <c r="O5">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="P5">
         <v>1.5E-3</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>1.9E-3</v>
       </c>
-      <c r="P5">
+      <c r="R5">
         <v>2E-3</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="S5">
-        <v>3.5999999999999999E-3</v>
-      </c>
-      <c r="T5">
-        <v>4.0000000000000001E-3</v>
       </c>
       <c r="U5">
         <v>3.5999999999999999E-3</v>
@@ -649,42 +1699,42 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="W5">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="X5" t="s">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="X5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Y5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Z5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="D6">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="F6">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>2E-3</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>1.9E-3</v>
       </c>
-      <c r="G6">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J6">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="I6">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="J6">
+      <c r="K6">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L6">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="K6">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="L6">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="M6">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="N6">
         <v>1.2999999999999999E-3</v>
@@ -705,7 +1755,7 @@
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="T6">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="U6">
         <v>1.2999999999999999E-3</v>
@@ -714,126 +1764,126 @@
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="W6">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="X6" t="s">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="X6">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Y6">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Z6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="D9">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="E9">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G9">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="F9">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="G9">
+      <c r="H9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I9">
         <v>2E-3</v>
       </c>
-      <c r="H9">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="I9">
+      <c r="J9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K9">
         <v>1.9E-3</v>
       </c>
-      <c r="J9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="K9">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="L9">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="M9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="N9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="O9">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="O9">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="P9">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="Q9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="R9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="S9">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="R9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="S9">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="T9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="U9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="V9">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="U9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="V9">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="W9">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="X9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Y9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Z9">
         <v>1.5E-3</v>
       </c>
-      <c r="Y9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Z9">
+      <c r="AA9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AB9">
         <v>1.9E-3</v>
       </c>
-      <c r="AA9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AB9">
+      <c r="AC9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AD9">
         <v>2E-3</v>
       </c>
-      <c r="AC9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AD9">
+      <c r="AE9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AF9">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="AE9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AF9">
+      <c r="AG9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AH9">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="AG9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AH9">
+      <c r="AI9">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AJ9">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="AI9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AJ9">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="AK9">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="AL9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AM9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AN9">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="AM9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AN9">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="AO9">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="AP9">
         <v>4.0000000000000001E-3</v>
@@ -841,972 +1891,1757 @@
       <c r="AQ9">
         <v>4.0000000000000001E-3</v>
       </c>
+      <c r="AR9">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AS9">
+        <v>4.0000000000000001E-3</v>
+      </c>
     </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="E11">
+    <row r="11" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G11">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J11">
         <v>2E-3</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M11">
         <v>1.9E-3</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="N11">
-        <v>4.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="P11">
-        <v>1.2999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="S11">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="T11">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
       <c r="V11">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Y11">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="Z11">
-        <v>4.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="AB11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="AC11">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
       <c r="AE11">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="AF11">
-        <v>1.2999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="AH11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
         <v>1.5E-3</v>
       </c>
-      <c r="AI11">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
       <c r="AK11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
         <v>1.9E-3</v>
       </c>
-      <c r="AL11">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
       <c r="AN11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
         <v>2E-3</v>
       </c>
-      <c r="AO11">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
       <c r="AQ11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="AR11">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
       <c r="AT11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="AU11">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
       <c r="AW11">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="AX11">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
       <c r="AZ11">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="BA11">
-        <v>4.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="BC11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="BD11">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="BE11">
-        <v>0</v>
-      </c>
       <c r="BF11">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="BG11">
-        <v>4.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="BI11">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="BJ11">
-        <v>4.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="BK11">
-        <v>0</v>
-      </c>
-      <c r="BL11" t="s">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BL11">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="E13">
+    <row r="13" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G13">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>0.2</v>
       </c>
-      <c r="G13">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J13">
         <v>2E-3</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>0.4</v>
       </c>
-      <c r="J13">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="K13">
+      <c r="L13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M13">
         <v>1.9E-3</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>0.6</v>
       </c>
-      <c r="M13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="N13">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="O13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="P13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Q13">
         <v>0.7</v>
       </c>
-      <c r="P13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q13">
+      <c r="R13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="S13">
         <v>3.8999999999999998E-3</v>
       </c>
-      <c r="R13">
+      <c r="T13">
         <v>0.8</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="T13">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="U13">
+      <c r="V13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="W13">
         <v>0.9</v>
       </c>
-      <c r="V13">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="W13">
+      <c r="X13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Y13">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="X13">
+      <c r="Z13">
         <v>1</v>
       </c>
-      <c r="Y13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Z13">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="AA13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AB13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AC13">
         <v>1.2</v>
       </c>
-      <c r="AB13">
+      <c r="AD13">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="AC13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AD13">
+      <c r="AE13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AF13">
         <v>1.4</v>
       </c>
-      <c r="AE13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AF13">
-        <v>1.2999999999999999E-3</v>
-      </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="AH13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
         <v>1.5E-3</v>
       </c>
-      <c r="AI13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
       <c r="AK13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
         <v>1.9E-3</v>
       </c>
-      <c r="AL13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
       <c r="AN13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
         <v>2E-3</v>
       </c>
-      <c r="AO13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
       <c r="AQ13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="AR13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
       <c r="AT13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="AU13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
       <c r="AW13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="AX13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
       <c r="AZ13">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="BA13">
-        <v>4.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="BC13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="BD13">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="BE13">
-        <v>0</v>
-      </c>
       <c r="BF13">
-        <v>4.0000000000000001E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="BG13">
-        <v>4.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="BI13">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="BJ13">
-        <v>4.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="BK13">
-        <v>0</v>
-      </c>
-      <c r="BL13" t="s">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BL13">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="D15">
         <f>-1.8411</f>
         <v>-1.8411</v>
       </c>
-      <c r="C15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15">
+      <c r="E15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <v>4.9917579159516898E-3</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>1.69595975098749E-3</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>1.53974225422019</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>4.9938175453636902E-3</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>1.52734599893879E-3</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>2.6425776191910102</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>4.99927311046202E-3</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>4.98549363194975E-3</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>1.38776431390161</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>4.9464215982714596E-3</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>4.2953197422253703E-3</v>
       </c>
-      <c r="O15">
+      <c r="Q15">
         <v>2.4093315068202998</v>
       </c>
-      <c r="P15">
+      <c r="R15">
         <v>1.8189321702073E-3</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
         <v>1.0583880824811701E-3</v>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>2.8841487871146998</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>2.3829718197879201E-3</v>
       </c>
-      <c r="T15">
+      <c r="V15">
         <v>2.2888507753033001E-3</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>1.2064090503867599</v>
       </c>
-      <c r="V15">
+      <c r="X15">
         <v>2.18903065690902E-3</v>
       </c>
-      <c r="W15">
+      <c r="Y15">
         <v>1.77999436998265E-3</v>
       </c>
-      <c r="X15">
+      <c r="Z15">
         <v>2.7574092757572499</v>
       </c>
-      <c r="Y15">
+      <c r="AA15">
         <v>1.00036787367038E-3</v>
       </c>
-      <c r="Z15">
+      <c r="AB15">
         <v>1.2211658668088701E-3</v>
       </c>
-      <c r="AA15">
+      <c r="AC15">
         <v>1.2277843263981199E-3</v>
       </c>
-      <c r="AB15">
+      <c r="AD15">
         <v>1.0004226815027899E-3</v>
       </c>
-      <c r="AC15">
+      <c r="AE15">
         <v>1.43424370261431E-3</v>
       </c>
-      <c r="AD15">
+      <c r="AF15">
         <v>2.6156269221677699</v>
       </c>
-      <c r="AE15">
+      <c r="AG15">
         <v>1.3631860047426799E-3</v>
       </c>
-      <c r="AF15">
+      <c r="AH15">
         <v>1.01709818146589E-3</v>
       </c>
-      <c r="AG15">
+      <c r="AI15">
         <v>1.17882694253418</v>
       </c>
-      <c r="AH15">
+      <c r="AJ15">
         <v>1.60603867362093E-3</v>
       </c>
-      <c r="AI15">
+      <c r="AK15">
         <v>1.2035585878934401E-3</v>
       </c>
-      <c r="AJ15">
+      <c r="AL15">
         <v>1.08236895450346</v>
       </c>
-      <c r="AK15">
+      <c r="AM15">
         <v>4.99361164120598E-3</v>
       </c>
-      <c r="AL15">
+      <c r="AN15">
         <v>1.7043963847344001E-3</v>
       </c>
-      <c r="AM15">
+      <c r="AO15">
         <v>1.6324039952234299</v>
       </c>
-      <c r="AN15">
+      <c r="AP15">
         <v>4.0604398977100503E-3</v>
       </c>
-      <c r="AO15">
+      <c r="AQ15">
         <v>1.0095972253412501E-3</v>
       </c>
-      <c r="AP15">
+      <c r="AR15">
         <v>1.0896067672312</v>
       </c>
-      <c r="AQ15">
+      <c r="AS15">
         <v>4.9928114567989899E-3</v>
       </c>
-      <c r="AR15">
+      <c r="AT15">
         <v>4.87339902093101E-3</v>
       </c>
-      <c r="AS15">
+      <c r="AU15">
         <v>0.927457951913082</v>
       </c>
-      <c r="AT15">
+      <c r="AV15">
         <v>4.9907424522168198E-3</v>
       </c>
-      <c r="AU15">
+      <c r="AW15">
         <v>4.9994982391283497E-3</v>
       </c>
-      <c r="AV15">
+      <c r="AX15">
         <v>2.41775361095609</v>
       </c>
-      <c r="AW15">
+      <c r="AY15">
         <v>4.9966924318709197E-3</v>
       </c>
-      <c r="AX15">
+      <c r="AZ15">
         <v>4.9981453308859001E-3</v>
       </c>
-      <c r="AY15">
+      <c r="BA15">
         <v>1.49562976361246</v>
       </c>
-      <c r="AZ15">
+      <c r="BB15">
         <v>4.7871529198324804E-3</v>
       </c>
-      <c r="BA15">
+      <c r="BC15">
         <v>4.9957628048072199E-3</v>
       </c>
-      <c r="BB15">
+      <c r="BD15">
         <v>2.7581032798254501</v>
       </c>
-      <c r="BC15">
+      <c r="BE15">
         <v>4.9932653830236703E-3</v>
       </c>
-      <c r="BD15">
+      <c r="BF15">
         <v>4.99747273573177E-3</v>
       </c>
-      <c r="BE15">
+      <c r="BG15">
         <v>2.2622097362276201</v>
       </c>
-      <c r="BF15">
+      <c r="BH15">
         <v>4.7896767299011904E-3</v>
       </c>
-      <c r="BG15">
+      <c r="BI15">
         <v>4.0944478477437001E-3</v>
       </c>
-      <c r="BH15">
+      <c r="BJ15">
         <v>0.28910723808435501</v>
       </c>
-      <c r="BI15">
+      <c r="BK15">
         <v>4.08738384131253E-3</v>
       </c>
-      <c r="BJ15">
+      <c r="BL15">
         <v>4.9994042539320202E-3</v>
       </c>
-      <c r="BK15">
+      <c r="BM15">
         <v>0.86791073471472502</v>
       </c>
-      <c r="BL15" t="s">
+      <c r="BN15" t="s">
         <v>2</v>
       </c>
-      <c r="BN15">
+      <c r="BP15">
         <f>-1.8411</f>
         <v>-1.8411</v>
       </c>
     </row>
-    <row r="17" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="1">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <f>ABS(D17)</f>
+        <v>2.0819999999999999</v>
+      </c>
+      <c r="D17" s="1">
         <v>-2.0819999999999999</v>
       </c>
-      <c r="C17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1">
+      <c r="E17" t="s">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
         <v>2.2720000000000001E-3</v>
       </c>
-      <c r="E17" s="1">
+      <c r="G17" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F17" s="1">
+      <c r="H17" s="1">
         <v>1.125</v>
       </c>
-      <c r="G17" s="1">
+      <c r="I17" s="1">
         <v>2.3340000000000001E-3</v>
       </c>
-      <c r="H17" s="1">
+      <c r="J17" s="1">
         <v>4.5669999999999999E-3</v>
       </c>
-      <c r="I17" s="1">
+      <c r="K17" s="1">
         <v>3.7940000000000002E-2</v>
       </c>
-      <c r="J17" s="1">
+      <c r="L17" s="1">
         <v>3.4190000000000002E-3</v>
       </c>
-      <c r="K17" s="1">
+      <c r="M17" s="1">
         <v>1.193E-3</v>
       </c>
-      <c r="L17" s="1">
+      <c r="N17" s="1">
         <v>2.161</v>
       </c>
-      <c r="M17" s="1">
+      <c r="O17" s="1">
         <v>1.841E-3</v>
       </c>
-      <c r="N17" s="1">
+      <c r="P17" s="1">
         <v>4.5189999999999996E-3</v>
       </c>
-      <c r="O17" s="1">
+      <c r="Q17" s="1">
         <v>0.54369999999999996</v>
       </c>
-      <c r="P17" s="1">
+      <c r="R17" s="1">
         <v>4.6109999999999996E-3</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="S17" s="1">
         <v>3.885E-3</v>
       </c>
-      <c r="R17" s="1">
+      <c r="T17" s="1">
         <v>2.09</v>
       </c>
-      <c r="S17" s="1">
+      <c r="U17" s="1">
         <v>2.085E-3</v>
       </c>
-      <c r="T17" s="1">
+      <c r="V17" s="1">
         <v>1.5659999999999999E-3</v>
       </c>
-      <c r="U17" s="1">
+      <c r="W17" s="1">
         <v>0.59470000000000001</v>
       </c>
-      <c r="V17" s="1">
+      <c r="X17" s="1">
         <v>1.1900000000000001E-3</v>
       </c>
-      <c r="W17" s="1">
+      <c r="Y17" s="1">
         <v>3.0969999999999999E-3</v>
       </c>
-      <c r="X17" s="1">
+      <c r="Z17" s="1">
         <v>1.867</v>
       </c>
-      <c r="Y17" s="1">
+      <c r="AA17" s="1">
         <v>1E-3</v>
       </c>
-      <c r="Z17" s="1">
+      <c r="AB17" s="1">
         <v>2.9320000000000001E-3</v>
       </c>
-      <c r="AA17" s="1">
+      <c r="AC17" s="1">
         <v>2.0539999999999998</v>
       </c>
-      <c r="AB17" s="1">
+      <c r="AD17" s="1">
         <v>1E-3</v>
       </c>
-      <c r="AC17" s="1">
+      <c r="AE17" s="1">
         <v>3.3449999999999999E-3</v>
       </c>
-      <c r="AD17" s="1">
+      <c r="AF17" s="1">
         <v>1.8759999999999999</v>
       </c>
-      <c r="AE17" s="1">
+      <c r="AG17" s="1">
         <v>1E-3</v>
       </c>
-      <c r="AF17" s="1">
+      <c r="AH17" s="1">
         <v>3.62E-3</v>
       </c>
-      <c r="AG17" s="1">
+      <c r="AI17" s="1">
         <v>2.0510000000000002</v>
       </c>
-      <c r="AH17" s="1">
+      <c r="AJ17" s="1">
         <v>4.5050000000000003E-3</v>
       </c>
-      <c r="AI17" s="1">
+      <c r="AK17" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AJ17" s="1">
+      <c r="AL17" s="1">
         <v>2.5649999999999999</v>
       </c>
-      <c r="AK17" s="1">
+      <c r="AM17" s="1">
         <v>4.8269999999999997E-3</v>
       </c>
-      <c r="AL17" s="1">
+      <c r="AN17" s="1">
         <v>4.0629999999999998E-3</v>
       </c>
-      <c r="AM17" s="1">
+      <c r="AO17" s="1">
         <v>1.7929999999999999</v>
       </c>
-      <c r="AN17" s="1">
+      <c r="AP17" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AO17" s="1">
+      <c r="AQ17" s="1">
         <v>4.8560000000000001E-3</v>
       </c>
-      <c r="AP17" s="1">
+      <c r="AR17" s="1">
         <v>3.0470000000000002</v>
       </c>
-      <c r="AQ17" s="1">
+      <c r="AS17" s="1">
         <v>4.6629999999999996E-3</v>
       </c>
-      <c r="AR17" s="1">
+      <c r="AT17" s="1">
         <v>2.8370000000000001E-3</v>
       </c>
-      <c r="AS17" s="1">
+      <c r="AU17" s="1">
         <v>2.4049999999999998</v>
       </c>
-      <c r="AT17" s="1">
+      <c r="AV17" s="1">
         <v>3.261E-3</v>
       </c>
-      <c r="AU17" s="1">
+      <c r="AW17" s="1">
         <v>4.3699999999999998E-3</v>
       </c>
-      <c r="AV17" s="1">
+      <c r="AX17" s="1">
         <v>1.845</v>
       </c>
-      <c r="AW17" s="1">
+      <c r="AY17" s="1">
         <v>2.3240000000000001E-3</v>
       </c>
-      <c r="AX17" s="1">
+      <c r="AZ17" s="1">
         <v>2.9780000000000002E-3</v>
       </c>
-      <c r="AY17" s="1">
+      <c r="BA17" s="1">
         <v>0.54490000000000005</v>
       </c>
-      <c r="AZ17" s="1">
+      <c r="BB17" s="1">
         <v>1E-3</v>
-      </c>
-      <c r="BA17" s="1">
-        <v>1E-3</v>
-      </c>
-      <c r="BB17" s="1">
-        <v>0.24940000000000001</v>
       </c>
       <c r="BC17" s="1">
         <v>1E-3</v>
       </c>
       <c r="BD17" s="1">
+        <v>0.24940000000000001</v>
+      </c>
+      <c r="BE17" s="1">
         <v>1E-3</v>
-      </c>
-      <c r="BE17" s="1">
-        <v>2.8889999999999998</v>
       </c>
       <c r="BF17" s="1">
         <v>1E-3</v>
       </c>
       <c r="BG17" s="1">
+        <v>2.8889999999999998</v>
+      </c>
+      <c r="BH17" s="1">
         <v>1E-3</v>
       </c>
-      <c r="BH17" s="1">
+      <c r="BI17" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BJ17" s="1">
         <v>0.27689999999999998</v>
       </c>
-      <c r="BI17" s="1">
+      <c r="BK17" s="1">
         <v>1.1349999999999999E-3</v>
       </c>
-      <c r="BJ17" s="1">
+      <c r="BL17" s="1">
         <v>1E-3</v>
       </c>
-      <c r="BK17" s="1">
+      <c r="BM17" s="1">
         <v>1.474</v>
       </c>
-      <c r="BL17" t="s">
+      <c r="BN17" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:64" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1">
+        <v>7</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <f>ABS(D19)</f>
+        <v>0.67</v>
+      </c>
+      <c r="D19" s="1">
         <v>-0.67</v>
       </c>
-      <c r="C19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1">
+      <c r="E19" t="s">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
         <v>4.8609999999999999E-3</v>
       </c>
-      <c r="E19" s="1">
+      <c r="G19" s="1">
         <v>2.9729999999999999E-3</v>
       </c>
-      <c r="F19" s="1">
+      <c r="H19" s="1">
         <v>2.4969999999999999</v>
       </c>
-      <c r="G19" s="1">
+      <c r="I19" s="1">
         <v>2.7460000000000002E-3</v>
       </c>
-      <c r="H19" s="1">
+      <c r="J19" s="1">
         <v>1.2769999999999999E-3</v>
       </c>
-      <c r="I19" s="1">
+      <c r="K19" s="1">
         <v>0.26290000000000002</v>
       </c>
-      <c r="J19" s="1">
+      <c r="L19" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K19" s="1">
+      <c r="M19" s="1">
         <v>2.0669999999999998E-3</v>
       </c>
-      <c r="L19" s="1">
+      <c r="N19" s="1">
         <v>2.8730000000000002</v>
       </c>
-      <c r="M19" s="1">
+      <c r="O19" s="1">
         <v>3.6280000000000001E-3</v>
       </c>
-      <c r="N19" s="1">
+      <c r="P19" s="1">
         <v>2.6900000000000001E-3</v>
       </c>
-      <c r="O19" s="1">
+      <c r="Q19" s="1">
         <v>1.8069999999999999</v>
       </c>
-      <c r="P19" s="1">
+      <c r="R19" s="1">
         <v>3.5729999999999998E-3</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="S19" s="1">
         <v>3.5729999999999998E-3</v>
       </c>
-      <c r="R19" s="1">
+      <c r="T19" s="1">
         <v>1.4630000000000001</v>
       </c>
-      <c r="S19" s="1">
+      <c r="U19" s="1">
         <v>4.3200000000000001E-3</v>
-      </c>
-      <c r="T19" s="1">
-        <v>2.6900000000000001E-3</v>
-      </c>
-      <c r="U19" s="1">
-        <v>2.069</v>
       </c>
       <c r="V19" s="1">
         <v>2.6900000000000001E-3</v>
       </c>
       <c r="W19" s="1">
+        <v>2.069</v>
+      </c>
+      <c r="X19" s="1">
+        <v>2.6900000000000001E-3</v>
+      </c>
+      <c r="Y19" s="1">
         <v>4.7169999999999998E-3</v>
       </c>
-      <c r="X19" s="1">
+      <c r="Z19" s="1">
         <v>1.2849999999999999</v>
       </c>
-      <c r="Y19" s="1">
+      <c r="AA19" s="1">
         <v>2.4529999999999999E-3</v>
-      </c>
-      <c r="Z19" s="1">
-        <v>1E-3</v>
-      </c>
-      <c r="AA19" s="1">
-        <v>2.278</v>
       </c>
       <c r="AB19" s="1">
         <v>1E-3</v>
       </c>
       <c r="AC19" s="1">
+        <v>2.278</v>
+      </c>
+      <c r="AD19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AE19" s="1">
         <v>3.176E-3</v>
       </c>
-      <c r="AD19" s="1">
+      <c r="AF19" s="1">
         <v>0.39779999999999999</v>
       </c>
-      <c r="AE19" s="1">
+      <c r="AG19" s="1">
         <v>4.8609999999999999E-3</v>
       </c>
-      <c r="AF19" s="1">
+      <c r="AH19" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AG19" s="1">
+      <c r="AI19" s="1">
         <v>0.68200000000000005</v>
       </c>
-      <c r="AH19" s="1">
+      <c r="AJ19" s="1">
         <v>1.0250000000000001E-3</v>
       </c>
-      <c r="AI19" s="1">
+      <c r="AK19" s="1">
         <v>3.3540000000000002E-3</v>
       </c>
-      <c r="AJ19" s="1">
+      <c r="AL19" s="1">
         <v>3.0339999999999998</v>
       </c>
-      <c r="AK19" s="1">
+      <c r="AM19" s="1">
         <v>4.8609999999999999E-3</v>
       </c>
-      <c r="AL19" s="1">
+      <c r="AN19" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AM19" s="1">
+      <c r="AO19" s="1">
         <v>2.9279999999999999</v>
       </c>
-      <c r="AN19" s="1">
+      <c r="AP19" s="1">
         <v>4.8609999999999999E-3</v>
       </c>
-      <c r="AO19" s="1">
+      <c r="AQ19" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AP19" s="1">
+      <c r="AR19" s="1">
         <v>0.63970000000000005</v>
       </c>
-      <c r="AQ19" s="1">
+      <c r="AS19" s="1">
         <v>3.5729999999999998E-3</v>
       </c>
-      <c r="AR19" s="1">
+      <c r="AT19" s="1">
         <v>3.5729999999999998E-3</v>
       </c>
-      <c r="AS19" s="1">
+      <c r="AU19" s="1">
         <v>1.375</v>
       </c>
-      <c r="AT19" s="1">
+      <c r="AV19" s="1">
         <v>1E-3</v>
-      </c>
-      <c r="AU19" s="1">
-        <v>1E-3</v>
-      </c>
-      <c r="AV19" s="1">
-        <v>1.9390000000000001</v>
       </c>
       <c r="AW19" s="1">
         <v>1E-3</v>
       </c>
       <c r="AX19" s="1">
+        <v>1.9390000000000001</v>
+      </c>
+      <c r="AY19" s="1">
         <v>1E-3</v>
-      </c>
-      <c r="AY19" s="1">
-        <v>1.208</v>
       </c>
       <c r="AZ19" s="1">
         <v>1E-3</v>
       </c>
       <c r="BA19" s="1">
+        <v>1.208</v>
+      </c>
+      <c r="BB19" s="1">
         <v>1E-3</v>
-      </c>
-      <c r="BB19" s="1">
-        <v>0.75949999999999995</v>
       </c>
       <c r="BC19" s="1">
         <v>1E-3</v>
       </c>
       <c r="BD19" s="1">
+        <v>0.75949999999999995</v>
+      </c>
+      <c r="BE19" s="1">
         <v>1E-3</v>
-      </c>
-      <c r="BE19" s="1">
-        <v>2.8410000000000002</v>
       </c>
       <c r="BF19" s="1">
         <v>1E-3</v>
       </c>
       <c r="BG19" s="1">
+        <v>2.8410000000000002</v>
+      </c>
+      <c r="BH19" s="1">
         <v>1E-3</v>
-      </c>
-      <c r="BH19" s="1">
-        <v>2.5339999999999998</v>
       </c>
       <c r="BI19" s="1">
         <v>1E-3</v>
       </c>
       <c r="BJ19" s="1">
+        <v>2.5339999999999998</v>
+      </c>
+      <c r="BK19" s="1">
         <v>1E-3</v>
       </c>
-      <c r="BK19" s="1">
+      <c r="BL19" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="BM19" s="1">
         <v>1.25</v>
       </c>
-      <c r="BL19" t="s">
+      <c r="BN19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="D21" s="1">
+        <v>-6.2229999999999999</v>
+      </c>
+      <c r="E21" t="s">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3.859E-3</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4.947E-3</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2.12</v>
+      </c>
+      <c r="I21" s="1">
+        <v>4.8859999999999997E-3</v>
+      </c>
+      <c r="J21" s="1">
+        <v>4.9540000000000001E-3</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1.1850000000000001</v>
+      </c>
+      <c r="L21" s="1">
+        <v>4.9329999999999999E-3</v>
+      </c>
+      <c r="M21" s="1">
+        <v>4.9329999999999999E-3</v>
+      </c>
+      <c r="N21" s="1">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="O21" s="1">
+        <v>1.1119999999999999E-3</v>
+      </c>
+      <c r="P21" s="1">
+        <v>3.8219999999999999E-3</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0.95140000000000002</v>
+      </c>
+      <c r="R21" s="1">
+        <v>3.862E-3</v>
+      </c>
+      <c r="S21" s="1">
+        <v>1.029E-3</v>
+      </c>
+      <c r="T21" s="1">
+        <v>2.4220000000000002</v>
+      </c>
+      <c r="U21" s="1">
+        <v>4.6800000000000001E-3</v>
+      </c>
+      <c r="V21" s="1">
+        <v>1.1360000000000001E-3</v>
+      </c>
+      <c r="W21" s="1">
+        <v>2.7989999999999999</v>
+      </c>
+      <c r="X21" s="1">
+        <v>1.1429999999999999E-3</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>4.666E-3</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>1.958</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>1.0989999999999999E-3</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>3.8140000000000001E-3</v>
+      </c>
+      <c r="AC21" s="1">
+        <v>2.4369999999999998</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>1.0020000000000001E-3</v>
+      </c>
+      <c r="AE21" s="1">
+        <v>3.8349999999999999E-3</v>
+      </c>
+      <c r="AF21" s="1">
+        <v>2.8620000000000001</v>
+      </c>
+      <c r="AG21" s="1">
+        <v>1.059E-3</v>
+      </c>
+      <c r="AH21" s="1">
+        <v>4.7390000000000002E-3</v>
+      </c>
+      <c r="AI21" s="1">
+        <v>6.1210000000000001E-2</v>
+      </c>
+      <c r="AJ21" s="1">
+        <v>1.0349999999999999E-3</v>
+      </c>
+      <c r="AK21" s="1">
+        <v>2.0920000000000001E-3</v>
+      </c>
+      <c r="AL21" s="1">
+        <v>2.6509999999999998</v>
+      </c>
+      <c r="AM21" s="1">
+        <v>2.1419999999999998E-3</v>
+      </c>
+      <c r="AN21" s="1">
+        <v>1.0529999999999999E-3</v>
+      </c>
+      <c r="AO21" s="1">
+        <v>1.149</v>
+      </c>
+      <c r="AP21" s="1">
+        <v>2.1229999999999999E-3</v>
+      </c>
+      <c r="AQ21" s="1">
+        <v>1.0330000000000001E-3</v>
+      </c>
+      <c r="AR21" s="1">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="AS21" s="1">
+        <v>2.1879999999999998E-3</v>
+      </c>
+      <c r="AT21" s="1">
+        <v>1.036E-3</v>
+      </c>
+      <c r="AU21" s="1">
+        <v>1.2090000000000001</v>
+      </c>
+      <c r="AV21" s="1">
+        <v>4.9829999999999996E-3</v>
+      </c>
+      <c r="AW21" s="1">
+        <v>4.9550000000000002E-3</v>
+      </c>
+      <c r="AX21" s="1">
+        <v>1.583</v>
+      </c>
+      <c r="AY21" s="1">
+        <v>4.8939999999999999E-3</v>
+      </c>
+      <c r="AZ21" s="1">
+        <v>4.9290000000000002E-3</v>
+      </c>
+      <c r="BA21" s="1">
+        <v>1.4690000000000001</v>
+      </c>
+      <c r="BB21" s="1">
+        <v>4.9449999999999997E-3</v>
+      </c>
+      <c r="BC21" s="1">
+        <v>4.9950000000000003E-3</v>
+      </c>
+      <c r="BD21" s="1">
+        <v>0.39350000000000002</v>
+      </c>
+      <c r="BE21" s="1">
+        <v>4.9709999999999997E-3</v>
+      </c>
+      <c r="BF21" s="1">
+        <v>4.9490000000000003E-3</v>
+      </c>
+      <c r="BG21" s="1">
+        <v>1.177</v>
+      </c>
+      <c r="BH21" s="1">
+        <v>4.934E-3</v>
+      </c>
+      <c r="BI21" s="1">
+        <v>4.9500000000000004E-3</v>
+      </c>
+      <c r="BJ21" s="1">
+        <v>1.456</v>
+      </c>
+      <c r="BK21" s="1">
+        <v>4.9690000000000003E-3</v>
+      </c>
+      <c r="BL21" s="1">
+        <v>4.9220000000000002E-3</v>
+      </c>
+      <c r="BM21" s="1">
+        <v>1.909</v>
+      </c>
+      <c r="BN21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="D23" s="1">
+        <v>-8.8390000000000004</v>
+      </c>
+      <c r="E23" t="s">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3.5130000000000001E-3</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4.986E-3</v>
+      </c>
+      <c r="H23" s="1">
+        <v>2.12</v>
+      </c>
+      <c r="I23" s="1">
+        <v>4.9690000000000003E-3</v>
+      </c>
+      <c r="J23" s="1">
+        <v>4.9870000000000001E-3</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1.38</v>
+      </c>
+      <c r="L23" s="1">
+        <v>4.9820000000000003E-3</v>
+      </c>
+      <c r="M23" s="1">
+        <v>4.9820000000000003E-3</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1.6539999999999999</v>
+      </c>
+      <c r="O23" s="1">
+        <v>1.2880000000000001E-3</v>
+      </c>
+      <c r="P23" s="1">
+        <v>2.565E-3</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>1.758</v>
+      </c>
+      <c r="R23" s="1">
+        <v>3.2919999999999998E-3</v>
+      </c>
+      <c r="S23" s="1">
+        <v>1.193E-3</v>
+      </c>
+      <c r="T23" s="1">
+        <v>2.6389999999999998</v>
+      </c>
+      <c r="U23" s="1">
+        <v>2.3519999999999999E-3</v>
+      </c>
+      <c r="V23" s="1">
+        <v>1.0369999999999999E-3</v>
+      </c>
+      <c r="W23" s="1">
+        <v>2.2930000000000001</v>
+      </c>
+      <c r="X23" s="1">
+        <v>2.7989999999999998E-3</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>3.9199999999999999E-3</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>1.86</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>1.0269999999999999E-3</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>1.7639999999999999E-3</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>2.0030000000000001</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>1.0009999999999999E-3</v>
+      </c>
+      <c r="AE23" s="1">
+        <v>1.7700000000000001E-3</v>
+      </c>
+      <c r="AF23" s="1">
+        <v>2.8580000000000001</v>
+      </c>
+      <c r="AG23" s="1">
+        <v>1.0820000000000001E-3</v>
+      </c>
+      <c r="AH23" s="1">
+        <v>2.0820000000000001E-3</v>
+      </c>
+      <c r="AI23" s="1">
+        <v>2.1770000000000001E-2</v>
+      </c>
+      <c r="AJ23" s="1">
+        <v>1.0089999999999999E-3</v>
+      </c>
+      <c r="AK23" s="1">
+        <v>1.431E-3</v>
+      </c>
+      <c r="AL23" s="1">
+        <v>2.585</v>
+      </c>
+      <c r="AM23" s="1">
+        <v>1.593E-3</v>
+      </c>
+      <c r="AN23" s="1">
+        <v>1.0139999999999999E-3</v>
+      </c>
+      <c r="AO23" s="1">
+        <v>1.1950000000000001</v>
+      </c>
+      <c r="AP23" s="1">
+        <v>1.354E-3</v>
+      </c>
+      <c r="AQ23" s="1">
+        <v>1.0089999999999999E-3</v>
+      </c>
+      <c r="AR23" s="1">
+        <v>1.282</v>
+      </c>
+      <c r="AS23" s="1">
+        <v>2.2829999999999999E-3</v>
+      </c>
+      <c r="AT23" s="1">
+        <v>1.01E-3</v>
+      </c>
+      <c r="AU23" s="1">
+        <v>1.052</v>
+      </c>
+      <c r="AV23" s="1">
+        <v>4.9950000000000003E-3</v>
+      </c>
+      <c r="AW23" s="1">
+        <v>3.7650000000000001E-3</v>
+      </c>
+      <c r="AX23" s="1">
+        <v>1.5640000000000001</v>
+      </c>
+      <c r="AY23" s="1">
+        <v>4.9709999999999997E-3</v>
+      </c>
+      <c r="AZ23" s="1">
+        <v>3.8240000000000001E-3</v>
+      </c>
+      <c r="BA23" s="1">
+        <v>1.4570000000000001</v>
+      </c>
+      <c r="BB23" s="1">
+        <v>4.9849999999999998E-3</v>
+      </c>
+      <c r="BC23" s="1">
+        <v>4.0379999999999999E-3</v>
+      </c>
+      <c r="BD23" s="1">
+        <v>0.4017</v>
+      </c>
+      <c r="BE23" s="1">
+        <v>4.9919999999999999E-3</v>
+      </c>
+      <c r="BF23" s="1">
+        <v>4.986E-3</v>
+      </c>
+      <c r="BG23" s="1">
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="BH23" s="1">
+        <v>4.9820000000000003E-3</v>
+      </c>
+      <c r="BI23" s="1">
+        <v>4.9870000000000001E-3</v>
+      </c>
+      <c r="BJ23" s="1">
+        <v>1.454</v>
+      </c>
+      <c r="BK23" s="1">
+        <v>4.2620000000000002E-3</v>
+      </c>
+      <c r="BL23" s="1">
+        <v>4.9789999999999999E-3</v>
+      </c>
+      <c r="BM23" s="1">
+        <v>1.9079999999999999</v>
+      </c>
+      <c r="BN23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="D25" s="1">
+        <v>-9.4130000000000003</v>
+      </c>
+      <c r="E25" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>2.1419999999999998E-3</v>
+      </c>
+      <c r="G25" s="1">
+        <v>4.6259999999999999E-3</v>
+      </c>
+      <c r="H25" s="1">
+        <v>2.12</v>
+      </c>
+      <c r="I25" s="1">
+        <v>4.3140000000000001E-3</v>
+      </c>
+      <c r="J25" s="1">
+        <v>4.9940000000000002E-3</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1.4179999999999999</v>
+      </c>
+      <c r="L25" s="1">
+        <v>4.6239999999999996E-3</v>
+      </c>
+      <c r="M25" s="1">
+        <v>4.9919999999999999E-3</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1.653</v>
+      </c>
+      <c r="O25" s="1">
+        <v>1.755E-3</v>
+      </c>
+      <c r="P25" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>0.8145</v>
+      </c>
+      <c r="R25" s="1">
+        <v>4.2240000000000003E-3</v>
+      </c>
+      <c r="S25" s="1">
+        <v>1.157E-3</v>
+      </c>
+      <c r="T25" s="1">
+        <v>2.9129999999999998</v>
+      </c>
+      <c r="U25" s="1">
+        <v>1.6149999999999999E-3</v>
+      </c>
+      <c r="V25" s="1">
+        <v>1.0169999999999999E-3</v>
+      </c>
+      <c r="W25" s="1">
+        <v>2.7170000000000001</v>
+      </c>
+      <c r="X25" s="1">
+        <v>2.3909999999999999E-3</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>4.509E-3</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>1.38</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>1.6659999999999999E-3</v>
+      </c>
+      <c r="AB25" s="1">
+        <v>2.1919999999999999E-3</v>
+      </c>
+      <c r="AC25" s="1">
+        <v>1.33</v>
+      </c>
+      <c r="AD25" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AE25" s="1">
+        <v>1.4220000000000001E-3</v>
+      </c>
+      <c r="AF25" s="1">
+        <v>2.7480000000000002</v>
+      </c>
+      <c r="AG25" s="1">
+        <v>1.0369999999999999E-3</v>
+      </c>
+      <c r="AH25" s="1">
+        <v>1.4920000000000001E-3</v>
+      </c>
+      <c r="AI25" s="1">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="AJ25" s="1">
+        <v>1.0039999999999999E-3</v>
+      </c>
+      <c r="AK25" s="1">
+        <v>2.0010000000000002E-3</v>
+      </c>
+      <c r="AL25" s="1">
+        <v>2.798</v>
+      </c>
+      <c r="AM25" s="1">
+        <v>1.9419999999999999E-3</v>
+      </c>
+      <c r="AN25" s="1">
+        <v>1.0070000000000001E-3</v>
+      </c>
+      <c r="AO25" s="1">
+        <v>0.5786</v>
+      </c>
+      <c r="AP25" s="1">
+        <v>3.3419999999999999E-3</v>
+      </c>
+      <c r="AQ25" s="1">
+        <v>1.0039999999999999E-3</v>
+      </c>
+      <c r="AR25" s="1">
+        <v>0.61160000000000003</v>
+      </c>
+      <c r="AS25" s="1">
+        <v>1.7099999999999999E-3</v>
+      </c>
+      <c r="AT25" s="1">
+        <v>1.0039999999999999E-3</v>
+      </c>
+      <c r="AU25" s="1">
+        <v>1.2410000000000001</v>
+      </c>
+      <c r="AV25" s="1">
+        <v>4.9979999999999998E-3</v>
+      </c>
+      <c r="AW25" s="1">
+        <v>2.2569999999999999E-3</v>
+      </c>
+      <c r="AX25" s="1">
+        <v>1.5449999999999999</v>
+      </c>
+      <c r="AY25" s="1">
+        <v>4.9870000000000001E-3</v>
+      </c>
+      <c r="AZ25" s="1">
+        <v>2.284E-3</v>
+      </c>
+      <c r="BA25" s="1">
+        <v>1.4430000000000001</v>
+      </c>
+      <c r="BB25" s="1">
+        <v>4.993E-3</v>
+      </c>
+      <c r="BC25" s="1">
+        <v>3.8899999999999998E-3</v>
+      </c>
+      <c r="BD25" s="1">
+        <v>0.40570000000000001</v>
+      </c>
+      <c r="BE25" s="1">
+        <v>4.9959999999999996E-3</v>
+      </c>
+      <c r="BF25" s="1">
+        <v>4.9940000000000002E-3</v>
+      </c>
+      <c r="BG25" s="1">
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="BH25" s="1">
+        <v>4.9919999999999999E-3</v>
+      </c>
+      <c r="BI25" s="1">
+        <v>4.9940000000000002E-3</v>
+      </c>
+      <c r="BJ25" s="1">
+        <v>1.454</v>
+      </c>
+      <c r="BK25" s="1">
+        <v>4.6639999999999997E-3</v>
+      </c>
+      <c r="BL25" s="1">
+        <v>4.9899999999999996E-3</v>
+      </c>
+      <c r="BM25" s="1">
+        <v>1.9079999999999999</v>
+      </c>
+      <c r="BN25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="D27" s="1">
+        <v>-11.39</v>
+      </c>
+      <c r="E27" t="s">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1.9550000000000001E-3</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2.9390000000000002E-3</v>
+      </c>
+      <c r="H27" s="1">
+        <v>2.12</v>
+      </c>
+      <c r="I27" s="1">
+        <v>4.9090000000000002E-3</v>
+      </c>
+      <c r="J27" s="1">
+        <v>4.999E-3</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1.417</v>
+      </c>
+      <c r="L27" s="1">
+        <v>4.9500000000000004E-3</v>
+      </c>
+      <c r="M27" s="1">
+        <v>4.999E-3</v>
+      </c>
+      <c r="N27" s="1">
+        <v>1.643</v>
+      </c>
+      <c r="O27" s="1">
+        <v>1.3699999999999999E-3</v>
+      </c>
+      <c r="P27" s="1">
+        <v>2.3969999999999998E-3</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0.89810000000000001</v>
+      </c>
+      <c r="R27" s="1">
+        <v>4.3839999999999999E-3</v>
+      </c>
+      <c r="S27" s="1">
+        <v>1.4790000000000001E-3</v>
+      </c>
+      <c r="T27" s="1">
+        <v>2.5059999999999998</v>
+      </c>
+      <c r="U27" s="1">
+        <v>3.444E-3</v>
+      </c>
+      <c r="V27" s="1">
+        <v>1.0369999999999999E-3</v>
+      </c>
+      <c r="W27" s="1">
+        <v>2.5859999999999999</v>
+      </c>
+      <c r="X27" s="1">
+        <v>1.9469999999999999E-3</v>
+      </c>
+      <c r="Y27" s="1">
+        <v>4.9350000000000002E-3</v>
+      </c>
+      <c r="Z27" s="1">
+        <v>1.292</v>
+      </c>
+      <c r="AA27" s="1">
+        <v>1.433E-3</v>
+      </c>
+      <c r="AB27" s="1">
+        <v>3.3349999999999999E-3</v>
+      </c>
+      <c r="AC27" s="1">
+        <v>0.86140000000000005</v>
+      </c>
+      <c r="AD27" s="1">
+        <v>1.0059999999999999E-3</v>
+      </c>
+      <c r="AE27" s="1">
+        <v>1.2019999999999999E-3</v>
+      </c>
+      <c r="AF27" s="1">
+        <v>2.2370000000000001</v>
+      </c>
+      <c r="AG27" s="1">
+        <v>1.0070000000000001E-3</v>
+      </c>
+      <c r="AH27" s="1">
+        <v>1.0820000000000001E-3</v>
+      </c>
+      <c r="AI27" s="1">
+        <v>0.1258</v>
+      </c>
+      <c r="AJ27" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AK27" s="1">
+        <v>1.668E-3</v>
+      </c>
+      <c r="AL27" s="1">
+        <v>2.4609999999999999</v>
+      </c>
+      <c r="AM27" s="1">
+        <v>1.766E-3</v>
+      </c>
+      <c r="AN27" s="1">
+        <v>1.0009999999999999E-3</v>
+      </c>
+      <c r="AO27" s="1">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="AP27" s="1">
+        <v>2.085E-3</v>
+      </c>
+      <c r="AQ27" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AR27" s="1">
+        <v>1.159</v>
+      </c>
+      <c r="AS27" s="1">
+        <v>2.287E-3</v>
+      </c>
+      <c r="AT27" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="AU27" s="1">
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="AV27" s="1">
+        <v>3.9420000000000002E-3</v>
+      </c>
+      <c r="AW27" s="1">
+        <v>1.534E-3</v>
+      </c>
+      <c r="AX27" s="1">
+        <v>1.202</v>
+      </c>
+      <c r="AY27" s="1">
+        <v>4.999E-3</v>
+      </c>
+      <c r="AZ27" s="1">
+        <v>1.523E-3</v>
+      </c>
+      <c r="BA27" s="1">
+        <v>1.2110000000000001</v>
+      </c>
+      <c r="BB27" s="1">
+        <v>4.999E-3</v>
+      </c>
+      <c r="BC27" s="1">
+        <v>3.382E-3</v>
+      </c>
+      <c r="BD27" s="1">
+        <v>0.46460000000000001</v>
+      </c>
+      <c r="BE27" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BF27" s="1">
+        <v>4.999E-3</v>
+      </c>
+      <c r="BG27" s="1">
+        <v>1.18</v>
+      </c>
+      <c r="BH27" s="1">
+        <v>4.9909999999999998E-3</v>
+      </c>
+      <c r="BI27" s="1">
+        <v>4.999E-3</v>
+      </c>
+      <c r="BJ27" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="BK27" s="1">
+        <v>3.9560000000000003E-3</v>
+      </c>
+      <c r="BL27" s="1">
+        <v>4.999E-3</v>
+      </c>
+      <c r="BM27" s="1">
+        <v>1.905</v>
+      </c>
+      <c r="BN27" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>